--- a/测试用例.xlsx
+++ b/测试用例.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -476,12 +476,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>验证注册用户在走完所有新客流程后，余额消耗至不足以支持继续开盒时（余额 &lt; $2），弹窗是否正确触发</t>
+          <t>验证用户注册后走完所有新客流程（触发过充值弹窗、开过注册免费盒、下载APP免费盒）后余额&lt;$2时触发弹窗</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -491,39 +491,33 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1.email：test@hapatest.com
- password：a123456789
-2.账户为新注册用户
-3.已开注册免费盒
-4.已触发过充值弹窗</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户
+3.已走完所有新客流程（触发过充值弹窗、开过注册免费盒、下载APP免费盒）</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1. 用户注册账号
-2. 进入 free 页
-3. 开启注册免费盒
-4. 开盒结果弹窗中选择出售开盒物品
-5. 完成引导流程中的付费开盒
-6. 确认账户余额消耗至不足 $2
-7. 查看弹窗是否触发</t>
+          <t>1. 用户完成所有新客流程后，确保账户余额小于$2
+2. 访问网站首页或free页</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>弹窗正确触发，显示邀请好友赚钱引导弹窗</t>
+          <t>正确触发弹窗</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>验证弹窗文案是否正确显示：Start Your Earnings（主标题），Invite friends and earn money now!（副标题），Over $6M paid to users</t>
+          <t>验证余额计算不包含盒柜中的物品价值</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -533,37 +527,33 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>1.email：test@hapatest.com
- password：a123456789
-2.账户为新注册用户
-3.已开注册免费盒
-4.已触发过充值弹窗
-5.账户余额 &lt; $2</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户已走完所有新客流程
+3.盒柜中有物品</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1. 触发弹窗显示
-2. 核验弹窗主标题文案
-3. 核验弹窗副标题文案
-4. 核验弹窗补充文案</t>
+          <t>1. 查看账户余额
+2. 核对余额计算是否包含盒柜物品价值</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>弹窗主标题显示：Start Your Earnings；副标题显示：Invite friends and earn money now!；补充文案显示：Over $6M paid to users</t>
+          <t>余额计算不包含盒柜中的物品价值</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>验证弹窗按钮是否正确显示：Get Started</t>
+          <t>验证用户首次进入首页或free页时正确触发弹窗</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -573,291 +563,289 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1.email：test@hapatest.com
- password：a123456789
-2.账户为新注册用户
-3.已开注册免费盒
-4.已触发过充值弹窗
-5.账户余额 &lt; $2</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户已走完所有新客流程
+3.账户余额&lt;$2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1. 触发弹窗显示
-2. 核验弹窗按钮文案</t>
+          <t>1. 用户首次进入首页或free页
+2. 查看是否触发弹窗</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>弹窗按钮正确显示：Get Started</t>
+          <t>正确触发弹窗</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>验证注册用户在走完所有新客流程后，余额大于等于 $2 时，弹窗不触发</t>
+          <t>验证用户先访问首页时在首页触发弹窗</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1.email：test@hapatest.com
- password：a123456789
-2.账户为新注册用户
-3.已开注册免费盒
-4.已触发过充值弹窗
-5.账户余额 &gt;= $2</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户已走完所有新客流程
+3.账户余额&lt;$2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1. 用户注册账号
-2. 进入 free 页
-3. 开启注册免费盒
-4. 开盒结果弹窗中选择出售开盒物品
-5. 完成引导流程中的付费开盒
-6. 确认账户余额 &gt;= $2
-7. 查看弹窗是否触发</t>
+          <t>1. 用户先访问首页
+2. 查看是否在首页触发弹窗</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>弹窗不触发</t>
+          <t>在首页触发弹窗</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>验证注册用户未触发过充值弹窗时，弹窗不触发</t>
+          <t>验证用户先访问free页时在free页触发弹窗</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1.email：test@hapatest.com
- password：a123456789
-2.账户为新注册用户
-3.已开注册免费盒
-4.未触发过充值弹窗</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户已走完所有新客流程
+3.账户余额&lt;$2</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1. 用户注册账号
-2. 进入 free 页
-3. 开启注册免费盒
-4. 确认未触发过充值弹窗
-5. 查看弹窗是否触发</t>
+          <t>1. 用户先访问free页
+2. 查看是否在free页触发弹窗</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>弹窗不触发</t>
+          <t>在free页触发弹窗</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>验证注册用户未开过注册免费盒时，弹窗不触发</t>
+          <t>验证余额刚好等于$2时不触发弹窗</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1.email：test@hapatest.com
- password：a123456789
-2.账户为新注册用户
-3.未开过注册免费盒</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户已走完所有新客流程
+3.账户余额刚好等于$2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1. 用户注册账号
-2. 确认未开过注册免费盒
-3. 查看弹窗是否触发</t>
+          <t>1. 确保账户余额刚好等于$2
+2. 访问网站首页或free页
+3. 查看是否触发弹窗</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>弹窗不触发</t>
+          <t>不触发弹窗</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>验证注册用户未下载APP免费盒时，弹窗不触发</t>
+          <t>验证余额$1.99时触发弹窗</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1. 账户为注册用户
-2. 用户未下载APP免费盒</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户已走完所有新客流程
+3.账户余额为$1.99</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1. 用户注册并登录账户
-2. 检查是否触发弹窗</t>
+          <t>1. 确保账户余额为$1.99
+2. 访问网站首页或free页
+3. 查看是否触发弹窗</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>弹窗不触发</t>
+          <t>正确触发弹窗</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>验证弹窗在Android上显示正常</t>
+          <t>验证弹窗在页面加载完成后正确弹出</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1. 账户为注册用户
-2. Android设备登录</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户已走完所有新客流程
+3.账户余额&lt;$2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1. 在Android设备上触发弹窗
-2. 核验弹窗样式</t>
+          <t>1. 访问网站首页或free页
+2. 等待页面加载完成
+3. 查看弹窗是否正确弹出</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>弹窗在Android上显示正常，样式符合设计稿</t>
+          <t>弹窗在页面加载完成后正确弹出</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>验证弹窗在iOS上显示正常</t>
+          <t>验证弹窗遮罩层覆盖整个页面且不可点击穿透</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1. 账户为注册用户
-2. iOS设备登录</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户已走完所有新客流程
+3.账户余额&lt;$2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1. 在iOS设备上触发弹窗
-2. 核验弹窗样式</t>
+          <t>1. 访问网站首页或free页触发弹窗
+2. 查看弹窗遮罩层是否覆盖整个页面
+3. 尝试点击遮罩层区域</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>弹窗在iOS上显示正常，样式符合设计稿</t>
+          <t>弹窗遮罩层覆盖整个页面且不可点击穿透</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>验证弹窗在浏览器上显示正常</t>
+          <t>验证弹窗居中展示</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1. 账户为注册用户
-2. 浏览器登录</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户已走完所有新客流程
+3.账户余额&lt;$2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1. 在浏览器上触发弹窗
-2. 核验弹窗样式</t>
+          <t>1. 访问网站首页或free页触发弹窗
+2. 查看弹窗是否居中展示</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>弹窗在浏览器上显示正常，样式符合设计稿</t>
+          <t>弹窗居中展示</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>验证新注册已首充用户在余额消耗至不足以支持下一次开盒时（余额 &lt; $2），且之前没有触发过老拉新弹窗的情况下，弹窗是否正确触发</t>
+          <t>验证弹窗仅触发一次，后续不再重复弹出</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -867,102 +855,104 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1. 账户为新注册用户
-2. 已完成首充
-3. 余额消耗至 &lt; $2
-4. 之前未触发过老拉新弹窗</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1. 使用新注册已首充账户登录
-2. 开盒消费至余额 &lt; $2
-3. 观察是否触发弹窗</t>
+          <t>1. 用户注册账号后进入网站首页
+2. 观察弹窗是否弹出
+3. 关闭弹窗后刷新页面或重新进入
+4. 观察弹窗是否再次弹出</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>弹窗正确触发</t>
+          <t>弹窗仅在首次触发一次，后续不再重复弹出</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>验证弹窗文案是否正确显示：Empty Balance? Earn Them!（主标题），Invite friends &amp; unbox without spending（副标题）</t>
+          <t>验证弹窗弹出时有适当的动画效果</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1. 账户为注册用户
-2. 满足弹窗触发条件</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1. 触发弹窗显示
-2. 核验弹窗文案</t>
+          <t>1. 用户注册账号后进入网站首页
+2. 观察弹窗弹出时的动画效果</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>弹窗主标题显示：Empty Balance? Earn Them!，副标题显示：Invite friends &amp; unbox without spending</t>
+          <t>弹窗弹出时有适当的动画效果，过渡流畅自然</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>验证弹窗按钮是否正确显示：Start Earning</t>
+          <t>验证主标题"Start Your Earnings"正确展示</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1. 账户为注册用户
-2. 满足弹窗触发条件</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1. 触发弹窗显示
-2. 核验弹窗按钮</t>
+          <t>1. 用户注册账号后进入网站首页
+2. 观察弹窗中主标题内容</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>弹窗按钮正确显示：Start Earning</t>
+          <t>主标题"Start Your Earnings"正确展示，无错别字</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>验证新注册已首充用户在余额大于等于 $2 时，弹窗不触发</t>
+          <t>验证副标题"Invite friends and earn money now!"正确展示</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -974,32 +964,30 @@
         <is>
           <t>1.email：7788@qq.com
  password：a123456789
-2.账户为新注册已首充用户
-3.账户余额大于等于 $2</t>
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1. 用户注册账号并完成首充
-2. 确保账户余额大于等于 $2
-3. 进入hapa首页观察弹窗</t>
+          <t>1. 用户注册账号后进入网站首页
+2. 观察弹窗中副标题内容</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>弹窗不触发</t>
+          <t>副标题"Invite friends and earn money now!"正确展示，无错别字</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>验证新注册已首充用户在之前已经触发过老拉新弹窗的情况下，弹窗不触发</t>
+          <t>验证辅助文案"Over $6M paid to users"正确展示</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1011,32 +999,30 @@
         <is>
           <t>1.email：7788@qq.com
  password：a123456789
-2.账户为新注册已首充用户
-3.之前已经触发过老拉新弹窗</t>
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1. 用户注册账号并完成首充
-2. 确保之前已经触发过老拉新弹窗
-3. 进入hapa首页观察弹窗</t>
+          <t>1. 用户注册账号后进入网站首页
+2. 观察弹窗中辅助文案内容</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>弹窗不触发</t>
+          <t>辅助文案"Over $6M paid to users"正确展示，无错别字</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>验证新注册用户未完成首充时，弹窗不触发</t>
+          <t>验证"Get Started"按钮正确展示</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1048,69 +1034,65 @@
         <is>
           <t>1.email：7788@qq.com
  password：a123456789
-2.账户为新注册用户
-3.账户未完成首充</t>
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1. 用户注册账号
-2. 确保账户未完成首充
-3. 进入hapa首页观察弹窗</t>
+          <t>1. 用户注册账号后进入网站首页
+2. 观察弹窗中"Get Started"按钮展示</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>弹窗不触发</t>
+          <t>"Get Started"按钮正确展示，文案清晰可点击</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>验证弹窗在Android上显示正常</t>
+          <t>验证文案无截断、无错位、无遮挡</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>1.email：7788@qq.com
  password：a123456789
-2.账户满足弹窗触发条件
-3.Android设备</t>
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1. 使用Android设备打开hapa网站
-2. 触发弹窗显示
-3. 核验弹窗样式</t>
+          <t>1. 用户注册账号后进入网站首页
+2. 检查弹窗中所有文案的展示效果</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>弹窗在Android上显示正常，样式符合设计稿</t>
+          <t>文案无截断、无错位、无遮挡，展示完整清晰</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>验证弹窗在iOS上显示正常</t>
+          <t>验证点击"Get Started"按钮跳转至老拉新推荐页面</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1122,103 +1104,100 @@
         <is>
           <t>1.email：7788@qq.com
  password：a123456789
-2.账户满足弹窗触发条件
-3.iOS设备</t>
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1. 使用iOS设备打开hapa网站
-2. 触发弹窗显示
-3. 核验弹窗样式</t>
+          <t>1. 用户注册账号后进入网站首页
+2. 点击弹窗中"Get Started"按钮</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>弹窗在iOS上显示正常，样式符合设计稿</t>
+          <t>成功跳转至老拉新推荐页面</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>验证弹窗在浏览器上显示正常</t>
+          <t>验证点击弹窗外部区域关闭弹窗</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t>1.email：7788@qq.com
  password：a123456789
-2.账户满足弹窗触发条件
-3.PC浏览器</t>
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1. 使用PC浏览器打开hapa网站
-2. 触发弹窗显示
-3. 核验弹窗样式</t>
+          <t>1. 用户注册账号后进入网站首页
+2. 点击弹窗外部区域</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>弹窗在浏览器上显示正常，样式符合设计稿</t>
+          <t>弹窗成功关闭</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>验证首页Banner主标题是否正确显示：Invite Friends.（小号字体）</t>
+          <t>验证点击关闭按钮（如有）关闭弹窗</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1.已注册账号
-2.正常登陆网站</t>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1. 进入hapa首页
-2. 查看Banner主标题内容和字体大小</t>
+          <t>1. 用户注册账号后进入网站首页
+2. 点击弹窗中的关闭按钮</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Banner主标题显示"Invite Friends."且为小号字体</t>
+          <t>弹窗成功关闭</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>验证首页Banner副标题是否正确显示：Earn Money Now.（大号字体）</t>
+          <t>验证关闭弹窗后不影响用户继续操作</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1228,272 +1207,291 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1.已注册账号
-2.正常登陆网站</t>
+          <t>1.email：test@hapatest.com
+ password：a123456789
+2.账户余额低于$2
+3.充值弹窗已弹出</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1. 进入hapa首页
-2. 查看Banner副标题内容和字体大小</t>
+          <t>1. 点击充值弹窗的关闭按钮</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Banner副标题显示"Earn Money Now."且为大号字体</t>
+          <t>弹窗被关闭，用户可继续正常操作网站功能</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>验证首页Banner CTA按钮是否正确显示：Start Earning</t>
+          <t>验证余额$0时触发弹窗</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1.已注册账号
-2.正常登陆网站</t>
+          <t>1.email：test@hapatest.com
+ password：a123456789
+2.账户余额为$0
+3.已完成注册免费盒开盒
+4.已完成APP免费盒开盒</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. 进入hapa首页
-2. 查看Banner CTA按钮文案</t>
+2. 观察页面弹窗情况</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Banner CTA按钮显示"Start Earning"</t>
+          <t>弹出充值弹窗引导用户充值</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>验证首页Banner在无网络情况下不显示</t>
+          <t>验证余额$1.99时触发弹窗</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1.已注册账号
-2.正常登陆网站</t>
+          <t>1.email：test@hapatest.com
+ password：a123456789
+2.账户余额为$1.99
+3.已完成注册免费盒开盒
+4.已完成APP免费盒开盒</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. 进入hapa首页
-2. 关闭网络连接
-3. 刷新页面查看Banner显示</t>
+2. 观察页面弹窗情况</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Banner在无网络情况下不显示</t>
+          <t>弹出充值弹窗引导用户充值</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>验证首页Banner在弱网络情况下加载超时提示</t>
+          <t>验证余额$2.00时不触发弹窗</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1.已注册账号
-2.正常登陆网站
-3.通过工具设置弱网（f12，fiddler）</t>
+          <t>1.email：test@hapatest.com
+ password：a123456789
+2.账户余额为$2.00
+3.已完成注册免费盒开盒
+4.已完成APP免费盒开盒</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1. 设置弱网环境
-2. 进入hapa首页
-3. 观察Banner加载情况</t>
+          <t>1. 进入hapa首页
+2. 观察页面弹窗情况</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Banner加载超时有相应提示</t>
+          <t>不弹出充值弹窗</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>验证首页Banner在Android上显示正常</t>
+          <t>验证余额$2.01时不触发弹窗</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1.已注册账号
-2.Android设备登陆网站</t>
+          <t>1.email：test@hapatest.com
+ password：a123456789
+2.账户余额为$2.01
+3.已完成注册免费盒开盒
+4.已完成APP免费盒开盒</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1. 使用Android设备进入hapa首页
-2. 核验Banner样式</t>
+          <t>1. 进入hapa首页
+2. 观察页面弹窗情况</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Banner在Android设备上显示正常</t>
+          <t>不弹出充值弹窗</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>验证首页Banner在iOS上显示正常</t>
+          <t>验证余额为负数（理论不可能场景）时的处理</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1.已注册账号
-2.iOS设备登陆网站</t>
+          <t>1.email：test@hapatest.com
+ password：a123456789
+2.通过数据库手动设置账户余额为负数
+3.已完成注册免费盒开盒
+4.已完成APP免费盒开盒</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1. 使用iOS设备进入hapa首页
-2. 核验Banner样式</t>
+          <t>1. 进入hapa首页
+2. 观察页面弹窗情况及系统处理</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Banner在iOS设备上显示正常</t>
+          <t>系统正常处理，弹出充值弹窗或按业务规则处理异常余额</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>验证首页Banner在浏览器上显示正常</t>
+          <t>验证未完成注册免费盒开盒时不触发弹窗</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1.已注册账号
-2.浏览器登陆网站</t>
+          <t>1.email：test@hapatest.com
+ password：a123456789
+2.新注册用户
+3.账户余额低于$2
+4.未完成注册免费盒开盒</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1. 使用浏览器进入hapa首页
-2. 核验Banner样式</t>
+          <t>1. 进入hapa首页
+2. 观察页面弹窗情况</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Banner在浏览器上显示正常</t>
+          <t>不弹出充值弹窗，引导用户完成注册免费盒开盒流程</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>验证首页Banner加载时间是否在合理范围内</t>
+          <t>验证未完成下载APP免费盒时不触发弹窗</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1.浏览器：Chrome
-2.网络正常</t>
+          <t>1.email：test@hapatest.com
+ password：a123456789
+2.已完成注册免费盒开盒
+3.账户余额低于$2
+4.未完成APP免费盒开盒</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. 进入hapa首页
-2. 观察Banner加载时间</t>
+2. 观察页面弹窗情况</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Banner加载时间在合理范围内（建议3秒内完成加载）</t>
+          <t>不弹出充值弹窗，引导用户完成APP免费盒开盒流程</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>验证首页Banner在高并发情况下不崩溃</t>
+          <t>验证未触发过充值弹窗时不触发弹窗</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1503,31 +1501,34 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1.浏览器：Chrome
-2.准备并发测试工具</t>
+          <t>1.email：test@hapatest.com
+ password：a123456789
+2.新注册用户
+3.账户余额低于$2
+4.从未触发过充值弹窗</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1. 模拟高并发场景，多用户同时访问首页
-2. 观察Banner显示情况</t>
+          <t>1. 进入hapa首页
+2. 观察页面弹窗情况</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Banner在高并发情况下正常显示，页面不崩溃</t>
+          <t>根据新客流程状态判断是否弹出相应引导弹窗</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>验证Total Referral Earnings（平台累计佣金）是否位于页面顶部</t>
+          <t>验证新客流程部分完成时的处理逻辑</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1537,167 +1538,176 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1.浏览器：Chrome
-2.已登录账号</t>
+          <t>1.email：test@hapatest.com
+ password：a123456789
+2.已完成部分新客流程步骤
+3.账户余额低于$2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1. 进入Earn Money页面
-2. 核验Total Referral Earnings模块位置</t>
+          <t>1. 进入hapa首页
+2. 观察页面弹窗情况</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Total Referral Earnings（平台累计佣金）位于页面顶部</t>
+          <t>系统根据新客流程完成状态，弹出对应引导弹窗，不会直接弹出充值弹窗</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>验证分享模块是否位于页面中部</t>
+          <t>验证首充后余额消耗至&lt;$2时触发弹窗</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1.浏览器：Chrome
-2.已登录账号</t>
+          <t>1.账号已完成首充
+2.账号未触发过此弹窗</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1. 进入Earn Money页面
-2. 核验分享模块位置</t>
+          <t>1. 完成首充流程
+2. 进行开盒等操作消耗余额至$2以下
+3. 进入首页或free页</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>分享模块位于页面中部</t>
+          <t>触发已首充用户弹窗</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>验证How It Works模块是否位于页面中部</t>
+          <t>验证余额计算不包含盒柜中的物品价值</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1.浏览器：Chrome
-2.已登录账号</t>
+          <t>1.账号已完成首充
+2.账号未触发过此弹窗
+3.盒柜中有物品</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1. 进入Earn Money页面
-2. 核验How It Works模块位置</t>
+          <t>1. 完成首充并开盒
+2. 将物品收下放入盒柜
+3. 核实账户余额
+4. 进入首页或free页观察是否触发弹窗</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>How It Works模块位于页面中部</t>
+          <t>余额计算仅统计账户余额，不包含盒柜物品价值；当账户余额&lt;$2时正确触发弹窗</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>验证Top Earners Leaderboard（通过榜单强化 Social Proof）是否位于页面底部</t>
+          <t>验证之前未触发过老拉新弹窗时才触发</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1.浏览器：Chrome
-2.已登录账号</t>
+          <t>1.账号已完成首充
+2.账号余额&lt;$2</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1. 进入Earn Money页面
-2. 核验Top Earners Leaderboard模块位置</t>
+          <t>1. 使用未触发过老拉新弹窗的账号登录
+2. 进入首页或free页
+3. 观察是否触发弹窗</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Top Earners Leaderboard（通过榜单强化 Social Proof）位于页面底部</t>
+          <t>未触发过老拉新弹窗的用户正确触发已首充用户弹窗</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>验证三个分享组件是否调整到视觉层级统一</t>
+          <t>验证用户首次进入首页或free页时正确触发弹窗</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1.测试账号已登录
-2.进入新客引导页面</t>
+          <t>1.账号已完成首充
+2.账号余额&lt;$2
+3.账号未触发过此弹窗</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1. 查看三个分享组件的视觉样式
-2. 对比三个组件的视觉层级</t>
+          <t>1. 使用符合条件的账号登录
+2. 首次进入首页或free页
+3. 观察弹窗触发情况</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>三个分享组件视觉层级统一，样式一致</t>
+          <t>用户首次进入首页或free页时正确触发弹窗</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>验证分享组件点击后是否正确跳转</t>
+          <t>验证用户先访问首页时在首页触发弹窗</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1707,205 +1717,216 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1.测试账号已登录
-2.进入新客引导页面</t>
+          <t>1.账号已完成首充
+2.账号余额&lt;$2
+3.账号未触发过此弹窗</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1. 点击第一个分享组件
-2. 验证跳转是否正确
-3. 返回页面后点击第二个分享组件
-4. 验证跳转是否正确
-5. 返回页面后点击第三个分享组件
-6. 验证跳转是否正确</t>
+          <t>1. 使用符合条件的账号登录
+2. 直接访问首页
+3. 观察弹窗触发位置</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>三个分享组件点击后均能正确跳转到对应页面</t>
+          <t>弹窗在首页正确触发</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>验证页面风格是否与主站风格一致</t>
+          <t>验证用户先访问free页时在free页触发弹窗</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1.测试账号已登录
-2.进入新客引导页面</t>
+          <t>1.账号已完成首充
+2.账号余额&lt;$2
+3.账号未触发过此弹窗</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1. 查看新客引导页面整体风格
-2. 与主站风格进行对比</t>
+          <t>1. 使用符合条件的账号登录
+2. 直接访问free页
+3. 观察弹窗触发位置</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>页面风格与主站风格保持一致</t>
+          <t>弹窗在free页正确触发</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>验证页面是否统一为深色UI风格</t>
+          <t>验证余额刚好等于$2时不触发弹窗</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1.测试账号已登录
-2.进入新客引导页面</t>
+          <t>1.账号已完成首充
+2.账号余额刚好等于$2
+3.账号未触发过此弹窗</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1. 查看页面UI配色
-2. 确认是否为深色风格</t>
+          <t>1. 使用符合条件的账号登录
+2. 进入首页或free页
+3. 观察是否触发弹窗</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>页面统一为深色UI风格</t>
+          <t>余额等于$2时不触发弹窗</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>验证页面减少大面积白色模块</t>
+          <t>验证已触发过未首充用户弹窗的用户不再触发已首充用户弹窗</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1.测试账号已登录
-2.进入新客引导页面</t>
+          <t>1.账号已触发过未首充用户弹窗
+2.账号已完成首充
+3.账号余额&lt;$2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1. 检查页面中是否存在大面积白色模块</t>
+          <t>1. 使用已触发过未首充用户弹窗的账号登录
+2. 进入首页或free页
+3. 观察是否触发已首充用户弹窗</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>页面无大面积白色模块，整体为深色风格</t>
+          <t>已触发过未首充用户弹窗的用户不再触发已首充用户弹窗</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>验证页面在无网络情况下不显示</t>
+          <t>验证弹窗在整个生命周期内仅触发一次</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1.测试账号已登录
-2.断开网络连接</t>
+          <t>1.账号已完成首充
+2.账号余额&lt;$2
+3.账号未触发过此弹窗</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1. 断开网络连接
-2. 尝试访问新客引导页面</t>
+          <t>1. 使用符合条件的账号登录
+2. 进入首页或free页触发弹窗
+3. 关闭弹窗后再次进入首页或free页
+4. 观察是否再次触发弹窗</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>页面在无网络情况下不显示</t>
+          <t>弹窗仅触发一次，后续不再重复触发</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>验证页面在弱网络情况下加载超时提示</t>
+          <t>验证用户关闭弹窗后记录已触发状态</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1.测试账号已登录
-2.通过工具设置弱网（f12，fiddler）</t>
+          <t>1.账号已完成首充
+2.账号余额&lt;$2
+3.账号未触发过此弹窗</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1. 设置弱网环境
-2. 访问新客引导页面
-3. 观察页面加载情况</t>
+          <t>1. 使用符合条件的账号登录
+2. 进入首页或free页触发弹窗
+3. 点击关闭按钮关闭弹窗
+4. 重新登录账号
+5. 再次进入首页或free页</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>弱网络情况下页面加载超时后显示超时提示</t>
+          <t>用户关闭弹窗后已触发状态被正确记录，不再重复触发</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>验证页面在Android上显示正常</t>
+          <t>验证主标题"Empty Balance? Earn Them!"正确展示</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1917,31 +1938,30 @@
         <is>
           <t>1.email：7788@qq.com
  password：a123456789
-2.账户为新用户
-3.安卓登陆</t>
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1. 进入hapa首页后等待几秒
-2. 核验页面样式</t>
+          <t>1. 触发弹窗显示
+2. 查看弹窗主标题</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>页面样式同设计稿一致，显示正常</t>
+          <t>主标题"Empty Balance? Earn Them!"正确展示</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>验证页面在iOS上显示正常</t>
+          <t>验证副标题"Invite friends &amp; unbox without spending"正确展示</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1953,31 +1973,30 @@
         <is>
           <t>1.email：7788@qq.com
  password：a123456789
-2.账户为新用户
-3.iOS登陆</t>
+2.账户为新用户</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1. 进入hapa首页后等待几秒
-2. 核验页面样式</t>
+          <t>1. 触发弹窗显示
+2. 查看弹窗副标题</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>页面样式同设计稿一致，显示正常</t>
+          <t>副标题"Invite friends &amp; unbox without spending"正确展示</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>新客流程优化</t>
+          <t>测试点</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>验证页面在浏览器上显示正常</t>
+          <t>验证"Start Earning"按钮正确展示</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1989,19 +2008,1455 @@
         <is>
           <t>1.email：7788@qq.com
  password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>1. 触发弹窗显示
+2. 查看弹窗中的"Start Earning"按钮</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>"Start Earning"按钮正确展示</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>验证文案无截断、无错位、无遮挡</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1. 触发弹窗显示
+2. 检查弹窗所有文案显示情况</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>所有文案完整显示，无截断、无错位、无遮挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>验证点击"Start Earning"按钮跳转至老拉新推荐页面</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>1. 触发弹窗显示
+2. 点击弹窗中的"Start Earning"按钮</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>成功跳转至老拉新推荐页面</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>验证点击弹窗外部区域关闭弹窗</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>1. 触发弹窗显示
+2. 点击弹窗外部区域</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>弹窗被关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>验证点击关闭按钮（如有）关闭弹窗</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1. 触发弹窗显示
+2. 点击弹窗中的关闭按钮</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>弹窗被关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>验证关闭弹窗后不影响用户继续操作</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>1. 触发弹窗显示
+2. 关闭弹窗
+3. 继续操作网站其他功能</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>用户可以正常继续操作，无异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>验证首充后余额$0时触发弹窗</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>1. 完成首充操作，确保余额为$0
+2. 查看是否弹出弹窗</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>弹窗正常触发，引导用户邀请好友</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>验证首充后余额$1.99时触发弹窗</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>1. 完成首充操作，确保余额为$1.99
+2. 查看是否弹出弹窗</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>弹窗正常触发，引导用户邀请好友</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>验证首充后余额$2.00时不触发弹窗</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>1.账户为新注册用户
+2.账户未进行过任何充值</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1. 点击网站顶部导航栏的充值按钮
+2. 充值弹窗中选择card支付方式
+3. 输入充值金额$2.00
+4. 点击top up按钮到卡号信息页
+5. 输入邮箱：test@hapatest.com
+6. 输入卡号：4111111111111111
+7. 输入卡的过期时间：12/29
+8. 输入code：998
+9. 输入name：muxi
+10. 点击top按钮完成充值
+11. 进入free页面或其他页面
+12. 观察是否触发充值引导弹窗</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>余额为$2.00时不触发充值引导弹窗</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>验证首充后余额$2.01时不触发弹窗</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>1.账户为新注册用户
+2.账户未进行过任何充值</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1. 点击网站顶部导航栏的充值按钮
+2. 充值弹窗中选择card支付方式
+3. 输入充值金额$2.01
+4. 点击top up按钮到卡号信息页
+5. 输入邮箱：test@hapatest.com
+6. 输入卡号：4111111111111111
+7. 输入卡的过期时间：12/29
+8. 输入code：998
+9. 输入name：muxi
+10. 点击top按钮完成充值
+11. 进入free页面或其他页面
+12. 观察是否触发充值引导弹窗</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>余额为$2.01时不触发充值引导弹窗</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>验证首充后立即消耗完余额触发弹窗</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>1.账户为新注册用户
+2.账户已完成首充</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1. 首充后立即进入盒子列表
+2. 选择开盒次数并付费开盒，将余额消耗完毕
+3. 等待开盒结果弹窗出现
+4. 选择收下或回收
+5. 观察是否触发充值引导弹窗</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>首充后立即消耗完余额时触发充值引导弹窗</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>验证首充后间隔较长时间消耗完余额触发弹窗</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>1.账户为新注册用户
+2.账户已完成首充
+3.首充后间隔较长时间</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>1. 首充后间隔较长时间（如24小时后）进入盒子列表
+2. 选择开盒次数并付费开盒，将余额消耗完毕
+3. 等待开盒结果弹窗出现
+4. 选择收下或回收
+5. 观察是否触发充值引导弹窗</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>首充后间隔较长时间消耗完余额时触发充值引导弹窗</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>验证多次小额充值后余额不足时触发弹窗</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>1.账户为新注册用户
+2.账户已进行多次小额充值</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1. 多次进行小额充值（如每次充值$1）
+2. 进入盒子列表选择开盒次数并付费开盒
+3. 将余额消耗至不足时观察是否触发充值引导弹窗</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>多次小额充值后余额不足时触发充值引导弹窗</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>验证不同渠道来源的用户匹配对应的referral channel</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>1.通过不同渠道链接访问网站
+2.账户为新注册用户</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1. 通过不同渠道链接（如不同referral参数）访问网站
+2. 注册新账号
+3. 进入free页开启注册免费盒
+4. 核验用户数据中referral channel字段</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>用户referral channel与来源渠道正确匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>验证网络断开时弹窗不弹出且不阻塞用户操作</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>1.账户为已注册用户
+2.余额不足触发条件满足</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入free页面
+2. 断开网络连接
+3. 尝试进行开盒或其他操作
+4. 观察是否触发充值引导弹窗及页面响应</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>网络断开时充值引导弹窗不弹出，不阻塞用户操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>验证网络恢复后弹窗正常触发</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>1.账户为已注册用户
+2.余额不足触发条件满足</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入free页面
+2. 断开网络连接
+3. 恢复网络连接
+4. 观察充值引导弹窗是否正常触发</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>网络恢复后充值引导弹窗正常触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>验证弹窗请求超时时的处理逻辑</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>1.账户为已注册用户
+2.余额不足触发条件满足
+3.通过工具设置弱网（f12，fiddler）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1. 设置网络延迟或超时环境
+2. 触发充值引导弹窗请求
+3. 观察请求超时时的处理逻辑</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>弹窗请求超时时有友好的错误提示或重试机制，不阻塞用户操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>验证用户余额数据获取失败时不阻塞用户操作</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>1.账户为已注册用户
+2.余额数据获取接口异常</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>1. 模拟余额数据获取接口返回异常或失败
+2. 进入free页面或其他页面
+3. 尝试进行开盒或其他操作
+4. 观察页面响应和充值引导弹窗行为</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>用户余额数据获取失败时不阻塞用户操作，页面正常响应</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>验证新客流程状态数据异常时的降级处理</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>1. 模拟新客流程状态数据返回异常</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>系统有合理的降级处理，不影响用户正常使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>验证首充状态数据异常时的降级处理</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>1. 模拟首充状态数据返回异常</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>系统有合理的降级处理，不影响用户正常使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>验证iOS设备上弹窗正常展示和交互</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
 2.账户为新用户
-3.浏览器登陆</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+3.iOS设备登录</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. 进入hapa首页后等待几秒
-2. 核验页面样式</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>页面样式同设计稿一致，显示正常</t>
+2. 核验弹窗展示和交互功能</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>弹窗正常展示，交互功能正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>验证Android设备上弹窗正常展示和交互</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户
+3.Android设备登录</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒
+2. 核验弹窗展示和交互功能</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>弹窗正常展示，交互功能正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>验证不同屏幕尺寸下弹窗自适应展示</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>1. 使用不同屏幕尺寸设备进入hapa首页
+2. 核验弹窗自适应展示效果</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>弹窗在不同屏幕尺寸下自适应展示正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>验证横屏/竖屏切换时弹窗展示正常</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页等待弹窗展示
+2. 切换横屏/竖屏方向
+3. 核验弹窗展示是否正常</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>弹窗在横屏/竖屏切换时展示正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>验证iOS低版本系统弹窗正常</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户
+3.iOS低版本系统设备</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒
+2. 核验弹窗样式和功能</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>弹窗在iOS低版本系统上展示和功能正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>验证Android低版本系统弹窗正常</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户
+3.Android低版本系统设备</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒
+2. 核验弹窗样式和功能</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>弹窗在Android低版本系统上展示和功能正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>验证最新系统版本弹窗正常</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户
+3.最新系统版本设备</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒
+2. 核验弹窗样式和功能</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>弹窗在最新系统版本上展示和功能正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>验证弹窗在1秒内完成加载展示</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页并计时
+2. 核验弹窗加载时间</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>弹窗在1秒内完成加载展示</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>验证弹窗动画流畅无卡顿</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒触发弹窗
+2. 观察弹窗动画效果</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>弹窗动画流畅，无卡顿现象</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>验证弹窗不影响页面其他功能性能</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒触发弹窗
+2. 关闭弹窗后操作页面其他功能</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>弹窗关闭后页面其他功能响应正常，性能无影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>验证多个弹窗触发条件同时满足时的优先级处理</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户
+3.设置多个弹窗触发条件同时满足</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页
+2. 触发多个弹窗条件同时满足
+3. 观察弹窗显示优先级</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>弹窗按优先级正确显示，不会出现多个弹窗重叠或错乱</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>验证用户快速切换页面时弹窗触发正确</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒触发弹窗
+2. 在弹窗显示前快速切换到其他页面</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>弹窗触发逻辑正确，不会出现弹窗错位或异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>验证弹窗不暴露用户敏感信息</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒触发弹窗
+2. 核验弹窗内容是否包含用户敏感信息</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>弹窗不显示用户密码、余额等敏感信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>验证弹窗跳转链接安全可靠</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒触发弹窗
+2. 点击弹窗中的跳转链接</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>跳转链接指向安全可靠的页面，无钓鱼或恶意跳转</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>验证弹窗相关接口有防刷机制</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户
+3.准备接口测试工具</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>1. 获取弹窗相关接口
+2. 频繁调用弹窗接口</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>接口有频率限制或防刷机制，异常请求被拦截</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>验证英文环境下文案展示正确</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户
+3.系统语言设置为英文</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒触发弹窗
+2. 核验弹窗文案内容</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>弹窗文案为英文且内容正确无误</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>验证文案长度变化时UI布局适配正常</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户
+3.准备不同长度的文案测试数据</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒触发弹窗
+2. 切换不同语言观察弹窗布局</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>弹窗UI布局自适应文案长度变化，不会出现文字截断或溢出</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>验证海外用户（主要市场）文案本地化正确</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>1.email：7788@qq.com
+ password：a123456789
+2.账户为新用户
+3.切换到海外主要市场语言环境</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入hapa首页后等待几秒触发弹窗
+2. 核验弹窗文案本地化内容</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>弹窗文案本地化翻译准确，符合当地语言习惯</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>验证图片资源加载失败时有兜底展示</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>1.账号已登录
+2.进入有图片展示的页面</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>1. 模拟图片资源加载失败场景（断网或图片链接失效）
+2. 查看页面图片展示情况</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>图片加载失败时有兜底图或占位图展示，页面布局正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>验证图片清晰度满足要求</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>1.账号已登录
+2.进入有图片展示的页面</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>1. 查看页面中各类图片资源
+2. 核对图片清晰度是否符合设计要求</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>图片清晰度满足要求，无明显模糊、锯齿或失真现象</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>测试点</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>验证图片在不同网络下加载速度</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>1.账号已登录
+2.进入有图片展示的页面
+3.准备网络模拟工具</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>1. 分别模拟正常网络、弱网（3G）、极弱网络环境
+2. 观察各网络环境下图片加载速度</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>正常网络下图片快速加载，弱网环境下有合理加载时间，极弱网络有loading提示</t>
         </is>
       </c>
     </row>
